--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IBA\Thesis\Implementation\Advancements-in-Ensemble-Learning\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B23E31-4A7B-4FB3-B257-E2261F647EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E108835-593C-4103-9854-6C6E3FBB501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C2C4D7A9-A02F-4765-9375-2B79B66B31F3}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="95">
   <si>
     <t>Datasets</t>
   </si>
@@ -257,6 +257,60 @@
   </si>
   <si>
     <t>Kmean using Elbow Method and removing PSO1</t>
+  </si>
+  <si>
+    <t>2m 22s</t>
+  </si>
+  <si>
+    <t>1m 18s</t>
+  </si>
+  <si>
+    <t>1m 11s</t>
+  </si>
+  <si>
+    <t>1m 22s</t>
+  </si>
+  <si>
+    <t>0m 41s</t>
+  </si>
+  <si>
+    <t>2m 8s</t>
+  </si>
+  <si>
+    <t>2m 46s</t>
+  </si>
+  <si>
+    <t>0m 54s</t>
+  </si>
+  <si>
+    <t>0m 49s</t>
+  </si>
+  <si>
+    <t>3m 3s</t>
+  </si>
+  <si>
+    <t>1m 45s</t>
+  </si>
+  <si>
+    <t>1m 28s</t>
+  </si>
+  <si>
+    <t>1m 36s</t>
+  </si>
+  <si>
+    <t>0m 44s</t>
+  </si>
+  <si>
+    <t>2m 31s</t>
+  </si>
+  <si>
+    <t>4m 25s</t>
+  </si>
+  <si>
+    <t>1m 42s</t>
+  </si>
+  <si>
+    <t>1m 14s</t>
   </si>
 </sst>
 </file>
@@ -970,7 +1024,7 @@
     <col min="19" max="19" width="8.88671875" style="15"/>
     <col min="22" max="22" width="8.88671875" style="15"/>
     <col min="25" max="25" width="8.88671875" style="15"/>
-    <col min="27" max="27" width="8.88671875" style="15"/>
+    <col min="27" max="27" width="8.88671875" style="15" customWidth="1"/>
     <col min="30" max="30" width="8.88671875" style="15"/>
     <col min="33" max="33" width="8.88671875" style="15"/>
     <col min="36" max="36" width="8.88671875" style="15"/>
@@ -1195,6 +1249,33 @@
       <c r="M3" s="15">
         <v>0.96350000000000002</v>
       </c>
+      <c r="N3">
+        <v>0.97080291970802901</v>
+      </c>
+      <c r="O3">
+        <v>0.96350364963503599</v>
+      </c>
+      <c r="P3">
+        <v>50.647596836090003</v>
+      </c>
+      <c r="Q3">
+        <v>0.96350365000000004</v>
+      </c>
+      <c r="R3">
+        <v>0.94890510900000002</v>
+      </c>
+      <c r="S3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T3">
+        <v>0.96350364963503599</v>
+      </c>
+      <c r="U3">
+        <v>0.96350364963503599</v>
+      </c>
+      <c r="V3" t="s">
+        <v>86</v>
+      </c>
       <c r="Z3">
         <v>0.92330000000000001</v>
       </c>
@@ -1278,6 +1359,33 @@
       <c r="M4" s="15">
         <v>0.98519999999999996</v>
       </c>
+      <c r="N4">
+        <v>0.89705882352941102</v>
+      </c>
+      <c r="O4">
+        <v>0.97058823529411697</v>
+      </c>
+      <c r="P4">
+        <v>29.425289392471299</v>
+      </c>
+      <c r="Q4">
+        <v>0.97058823500000002</v>
+      </c>
+      <c r="R4">
+        <v>0.97058823500000002</v>
+      </c>
+      <c r="S4" t="s">
+        <v>78</v>
+      </c>
+      <c r="T4">
+        <v>0.92647058823529405</v>
+      </c>
+      <c r="U4">
+        <v>0.95588235294117596</v>
+      </c>
+      <c r="V4" t="s">
+        <v>87</v>
+      </c>
       <c r="Z4">
         <v>0.79410000000000003</v>
       </c>
@@ -1361,6 +1469,33 @@
       <c r="M5" s="15">
         <v>0.77039999999999997</v>
       </c>
+      <c r="N5">
+        <v>0.75409836065573699</v>
+      </c>
+      <c r="O5">
+        <v>0.786885245901639</v>
+      </c>
+      <c r="P5">
+        <v>29.204375743865899</v>
+      </c>
+      <c r="Q5">
+        <v>0.77049180299999998</v>
+      </c>
+      <c r="R5">
+        <v>0.704918033</v>
+      </c>
+      <c r="S5" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5">
+        <v>0.70491803278688503</v>
+      </c>
+      <c r="U5">
+        <v>0.62295081967213095</v>
+      </c>
+      <c r="V5" t="s">
+        <v>88</v>
+      </c>
       <c r="Z5">
         <v>0.73770000000000002</v>
       </c>
@@ -1444,6 +1579,33 @@
       <c r="M6" s="15">
         <v>0.92949999999999999</v>
       </c>
+      <c r="N6">
+        <v>0.676056338028169</v>
+      </c>
+      <c r="O6">
+        <v>0.63380281690140805</v>
+      </c>
+      <c r="P6">
+        <v>30.364363193511899</v>
+      </c>
+      <c r="Q6">
+        <v>0.85915492999999998</v>
+      </c>
+      <c r="R6">
+        <v>0.84507042300000002</v>
+      </c>
+      <c r="S6" t="s">
+        <v>80</v>
+      </c>
+      <c r="T6">
+        <v>0.88732394366197098</v>
+      </c>
+      <c r="U6">
+        <v>0.84507042253521103</v>
+      </c>
+      <c r="V6" t="s">
+        <v>89</v>
+      </c>
       <c r="Z6">
         <v>0.87319999999999998</v>
       </c>
@@ -1527,6 +1689,33 @@
       <c r="M7" s="15">
         <v>1</v>
       </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>15.2599327564239</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7" t="s">
+        <v>81</v>
+      </c>
+      <c r="T7">
+        <v>0.76666666666666605</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7" t="s">
+        <v>90</v>
+      </c>
       <c r="Z7">
         <v>1</v>
       </c>
@@ -1610,6 +1799,33 @@
       <c r="M8" s="15">
         <v>0.79479999999999995</v>
       </c>
+      <c r="N8">
+        <v>0.73504273504273498</v>
+      </c>
+      <c r="O8">
+        <v>0.75213675213675202</v>
+      </c>
+      <c r="P8">
+        <v>153.60872840881299</v>
+      </c>
+      <c r="Q8">
+        <v>0.743589744</v>
+      </c>
+      <c r="R8">
+        <v>0.75213675199999996</v>
+      </c>
+      <c r="S8" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8">
+        <v>0.75213675213675202</v>
+      </c>
+      <c r="U8">
+        <v>0.74358974358974295</v>
+      </c>
+      <c r="V8" t="s">
+        <v>91</v>
+      </c>
       <c r="Z8">
         <v>0.72219999999999995</v>
       </c>
@@ -1693,6 +1909,33 @@
       <c r="M9" s="15">
         <v>0.75319999999999998</v>
       </c>
+      <c r="N9">
+        <v>0.74675324675324595</v>
+      </c>
+      <c r="O9">
+        <v>0.60389610389610304</v>
+      </c>
+      <c r="P9">
+        <v>90.304743528366004</v>
+      </c>
+      <c r="Q9">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="R9">
+        <v>0.64285714299999996</v>
+      </c>
+      <c r="S9" t="s">
+        <v>83</v>
+      </c>
+      <c r="T9">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="U9">
+        <v>0.68831168831168799</v>
+      </c>
+      <c r="V9" t="s">
+        <v>92</v>
+      </c>
       <c r="Z9">
         <v>0.75</v>
       </c>
@@ -1776,6 +2019,33 @@
       <c r="M10" s="15">
         <v>0.90469999999999995</v>
       </c>
+      <c r="N10">
+        <v>0.76190476190476097</v>
+      </c>
+      <c r="O10">
+        <v>0.76190476190476097</v>
+      </c>
+      <c r="P10">
+        <v>20.101543664932201</v>
+      </c>
+      <c r="Q10">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="R10">
+        <v>0.73809523799999999</v>
+      </c>
+      <c r="S10" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10">
+        <v>0.952380952380952</v>
+      </c>
+      <c r="U10">
+        <v>0.76190476190476097</v>
+      </c>
+      <c r="V10" t="s">
+        <v>93</v>
+      </c>
       <c r="Z10">
         <v>0.83330000000000004</v>
       </c>
@@ -1858,6 +2128,33 @@
       </c>
       <c r="M11" s="15">
         <v>1</v>
+      </c>
+      <c r="N11">
+        <v>0.97222222222222199</v>
+      </c>
+      <c r="O11">
+        <v>0.77777777777777701</v>
+      </c>
+      <c r="P11">
+        <v>18.790242195129299</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11" t="s">
+        <v>85</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11" t="s">
+        <v>94</v>
       </c>
       <c r="Z11">
         <v>0.98609999999999998</v>
